--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486273_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486273_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.6241</v>
+        <v>12.3312</v>
       </c>
       <c r="E2" t="n">
-        <v>11.8041</v>
+        <v>11.3571</v>
       </c>
       <c r="F2" t="n">
-        <v>0.82</v>
+        <v>0.9742</v>
       </c>
       <c r="G2" t="n">
         <v>10.2107</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0208</v>
+        <v>0.7279</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8736</v>
+        <v>0.4266</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1472</v>
+        <v>0.3013</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1377</v>
+        <v>6.1511</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9325</v>
+        <v>4.0385</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2051</v>
+        <v>2.1127</v>
       </c>
       <c r="G3" t="n">
         <v>4.5</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>1.92</v>
+        <v>0.9334</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5502</v>
+        <v>0.6561</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3698</v>
+        <v>0.2773</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3698</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2661</v>
+        <v>5.1621</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6839</v>
+        <v>3.7956</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5823</v>
+        <v>1.3665</v>
       </c>
       <c r="G4" t="n">
         <v>4.29</v>
@@ -766,13 +766,13 @@
         <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3236</v>
+        <v>0.2196</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7346</v>
+        <v>0.5188</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8556</v>
+        <v>1.7727</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.7565</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7696</v>
+        <v>1.0162</v>
       </c>
       <c r="G5" t="n">
         <v>0.708</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8306</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.548</v>
+        <v>0.1226</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2826</v>
+        <v>-0.0361</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5443</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>J. GONZALEZ CALVO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4503</v>
+        <v>0.4853</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2405</v>
+        <v>-0.3143</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7902</v>
+        <v>0.7996</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0456</v>
+        <v>0.1199</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5202</v>
+        <v>-0.0092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5658</v>
+        <v>0.1291</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1804</v>
+        <v>0.6387</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1277</v>
+        <v>0.6387</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0527</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1348</v>
+        <v>-0.5188</v>
       </c>
       <c r="N6" t="n">
         <v>-0.6479</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4869</v>
+        <v>0.1291</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7947</v>
+        <v>0.0403</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0601</v>
+        <v>-0.256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7346</v>
+        <v>0.2962</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.695</v>
+        <v>0.7602</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.695</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3592</v>
+        <v>0.3463</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4517</v>
+        <v>1.3523</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8108</v>
+        <v>-1.0059</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8212</v>
+        <v>0.0456</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.375</v>
+        <v>-0.5202</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5538</v>
+        <v>0.5658</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9828</v>
+        <v>1.1804</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1741</v>
+        <v>0.1277</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1912</v>
+        <v>1.0527</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1617</v>
+        <v>-1.1348</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2009</v>
+        <v>-0.6479</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3626</v>
+        <v>-0.4869</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3533</v>
+        <v>0.6907</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6187</v>
+        <v>0.1719</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7346</v>
+        <v>0.5188</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3904</v>
+        <v>-1.695</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3904</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2842</v>
+        <v>-0.4271</v>
       </c>
       <c r="E8" t="n">
-        <v>1.502</v>
+        <v>-2.3927</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2179</v>
+        <v>1.9656</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7782</v>
+        <v>-0.9003</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5998</v>
+        <v>-1.5967</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8216</v>
+        <v>0.6965</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5702</v>
+        <v>-1.1105</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6538</v>
+        <v>-0.9974</v>
       </c>
       <c r="L8" t="n">
-        <v>1.224</v>
+        <v>-0.1131</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3484</v>
+        <v>0.2102</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9459</v>
+        <v>-0.5994</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4024</v>
+        <v>0.8096</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9971</v>
+        <v>0.2557</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8242</v>
+        <v>-0.1947</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1729</v>
+        <v>0.4503</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GONZALEZ CALVO</t>
+          <t>S. UGOCHUKWU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2002</v>
+        <v>-0.6127</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.434</v>
       </c>
       <c r="F9" t="n">
-        <v>0.738</v>
+        <v>-0.1787</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1199</v>
+        <v>-1.2711</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0092</v>
+        <v>-1.1221</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1291</v>
+        <v>-0.149</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6387</v>
+        <v>-0.7188</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6387</v>
+        <v>-0.7387</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0199</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5188</v>
+        <v>-0.5523</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6479</v>
+        <v>-0.3834</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1291</v>
+        <v>-0.1689</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2449</v>
+        <v>0.2659</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4795</v>
+        <v>0.2848</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2346</v>
+        <v>-0.0189</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7602</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. UGOCHUKWU</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0173</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9928</v>
+        <v>-2.4575</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0246</v>
+        <v>1.5951</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2711</v>
+        <v>-1.8212</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1221</v>
+        <v>-2.375</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.149</v>
+        <v>0.5538</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7188</v>
+        <v>-1.9828</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7387</v>
+        <v>-2.1741</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0199</v>
+        <v>0.1912</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5523</v>
+        <v>0.1617</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3834</v>
+        <v>-0.2009</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1689</v>
+        <v>0.3626</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1388</v>
+        <v>1.1317</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>0.6129</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1352</v>
+        <v>0.5188</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.14</v>
+        <v>-0.8642</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9515</v>
+        <v>0.3845</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8115</v>
+        <v>-1.2487</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9003</v>
+        <v>-0.7782</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5967</v>
+        <v>-1.5998</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6965</v>
+        <v>0.8216</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1105</v>
+        <v>0.5702</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9974</v>
+        <v>-0.6538</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1131</v>
+        <v>1.224</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2102</v>
+        <v>-1.3484</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5994</v>
+        <v>-0.9459</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8096</v>
+        <v>-0.4024</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4572</v>
+        <v>0.8487</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.7066</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2962</v>
+        <v>0.1421</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9542</v>
+        <v>-1.7943</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2778</v>
+        <v>-1.2719</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6765</v>
+        <v>-0.5223</v>
       </c>
       <c r="G12" t="n">
         <v>-5.8977</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9043</v>
+        <v>0.2557</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.2524</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1508</v>
+        <v>0.0033</v>
       </c>
       <c r="V12" t="n">
         <v>1.8902</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2448</v>
+        <v>-3.8672</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3731</v>
+        <v>-3.1496</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8717</v>
+        <v>-0.7176</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6989</v>
@@ -1468,13 +1468,13 @@
         <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1268</v>
+        <v>0.5044</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1286</v>
+        <v>0.3521</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0018</v>
+        <v>0.1523</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4552</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.8211</v>
+        <v>17.8208</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6643</v>
+        <v>11.6645</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1564</v>
+        <v>6.156700000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>7.506799999999998</v>
+        <v>7.5068</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.732999999999999</v>
+        <v>-1.732999999999998</v>
       </c>
       <c r="I14" t="n">
         <v>9.239700000000003</v>
@@ -1549,10 +1549,10 @@
         <v>5.9605</v>
       </c>
       <c r="T14" t="n">
-        <v>2.835900000000001</v>
+        <v>2.8361</v>
       </c>
       <c r="U14" t="n">
-        <v>3.1245</v>
+        <v>3.1242</v>
       </c>
       <c r="V14" t="n">
         <v>-5.433999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9064</v>
+        <v>4.2031</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8849</v>
+        <v>1.9966</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0215</v>
+        <v>2.2065</v>
       </c>
       <c r="G15" t="n">
         <v>4.8936</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7023</v>
+        <v>-0.4056</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0858</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>1.8902</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5437</v>
+        <v>0.7171</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2216</v>
+        <v>0.3334</v>
       </c>
       <c r="F16" t="n">
-        <v>0.322</v>
+        <v>0.3837</v>
       </c>
       <c r="G16" t="n">
         <v>1.3814</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7725</v>
+        <v>-0.599</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3615</v>
+        <v>-0.2998</v>
       </c>
       <c r="V16" t="n">
         <v>0.3698</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6622</v>
+        <v>-0.2113</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3772</v>
+        <v>-1.2654</v>
       </c>
       <c r="F17" t="n">
-        <v>0.715</v>
+        <v>1.0541</v>
       </c>
       <c r="G17" t="n">
         <v>-0.556</v>
@@ -1780,13 +1780,13 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.5477</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.519</v>
+        <v>-0.18</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6952</v>
+        <v>-0.3253</v>
       </c>
       <c r="E18" t="n">
         <v>-1.3216</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6264</v>
+        <v>0.9963</v>
       </c>
       <c r="G18" t="n">
         <v>0.3208</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.711</v>
+        <v>-1.3411</v>
       </c>
       <c r="T18" t="n">
         <v>-0.6165</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0945</v>
+        <v>-0.7246</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8756</v>
+        <v>-0.9951</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2064</v>
+        <v>0.8711</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.082</v>
+        <v>-1.8662</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6787</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1746</v>
+        <v>-0.2941</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1286</v>
+        <v>-0.2067</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3032</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>1.3252</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8523</v>
+        <v>-1.4978</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2443</v>
+        <v>1.6914</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0967</v>
+        <v>-3.1891</v>
       </c>
       <c r="G20" t="n">
         <v>0.21</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8872</v>
+        <v>-0.5327</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2708</v>
+        <v>-0.3632</v>
       </c>
       <c r="V20" t="n">
         <v>0.5649999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9936</v>
+        <v>-2.8837</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5579</v>
+        <v>-2.8932</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5643</v>
+        <v>0.0095</v>
       </c>
       <c r="G21" t="n">
         <v>0.1559</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6335</v>
+        <v>-0.2566</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.3437</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6419</v>
+        <v>0.0871</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3904</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4356</v>
+        <v>-3.2795</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7572</v>
+        <v>-2.5395</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6783</v>
+        <v>-0.74</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3445</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6919</v>
+        <v>-0.152</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9421</v>
+        <v>0.1598</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2502</v>
+        <v>-0.3118</v>
       </c>
       <c r="V22" t="n">
         <v>0.7395</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7352</v>
+        <v>-3.6312</v>
       </c>
       <c r="E23" t="n">
-        <v>2.7201</v>
+        <v>2.6084</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.4553</v>
+        <v>-6.2395</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7368</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9761</v>
+        <v>-0.8721</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0769</v>
+        <v>-0.1887</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8992</v>
+        <v>-0.6835</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3698</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4898</v>
+        <v>-4.1853</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7747</v>
+        <v>-2.4394</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7151</v>
+        <v>-1.7459</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1674</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6046</v>
+        <v>-0.3001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4795</v>
+        <v>-0.1442</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1251</v>
+        <v>-0.1559</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1952</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5317</v>
+        <v>-5.732</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6454</v>
+        <v>-3.1984</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8863</v>
+        <v>-2.5336</v>
       </c>
       <c r="G25" t="n">
         <v>-4.985</v>
@@ -2404,13 +2404,13 @@
         <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4592</v>
+        <v>-0.6594</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4313</v>
+        <v>-0.216</v>
       </c>
       <c r="V25" t="n">
         <v>0.5649999999999999</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.8211</v>
+        <v>-17.821</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.156700000000001</v>
+        <v>-6.156600000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.6645</v>
+        <v>-11.6642</v>
       </c>
       <c r="G26" t="n">
         <v>-7.5067</v>
@@ -2482,13 +2482,13 @@
         <v>7.612499999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.9606</v>
+        <v>-5.960399999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.1245</v>
+        <v>-3.1244</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8361</v>
+        <v>-2.836</v>
       </c>
       <c r="V26" t="n">
         <v>5.434100000000001</v>
